--- a/BOP PLC_IO List  v0.5.xlsx
+++ b/BOP PLC_IO List  v0.5.xlsx
@@ -2576,7 +2576,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Kyle Howard" id="{74150FB0-E1E1-431D-876B-46062C37FCAC}" userId="S::kyle.howard@casne.com::64e8ec0d-0962-43b9-9c19-fa9309dce3f5" providerId="AD"/>
+  <person displayName="Kyle Howard" id="{74150FB0-E1E1-431D-876B-46062C37FCAC}" userId="S::[REDACTED]::64e8ec0d-0962-43b9-9c19-fa9309dce3f5" providerId="AD"/>
 </personList>
 </file>
 
